--- a/InputFiles/CDS/CCDI basecounts.xlsx
+++ b/InputFiles/CDS/CCDI basecounts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\davids3\CRDC_CLI\git\Sofia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\davids3\CRDC_CLI\GC_2026_Sof\Commons_Automation\InputFiles\CDS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0424968F-DCF6-4E57-A75C-4970DE602CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25274C0-587F-43DC-8F4D-3FCB834CF582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{CD5F72A1-F206-4A66-B751-69F616B63075}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CD5F72A1-F206-4A66-B751-69F616B63075}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="43">
   <si>
     <t>Study</t>
   </si>
@@ -156,13 +156,22 @@
   </si>
   <si>
     <t>phs004217</t>
+  </si>
+  <si>
+    <t>Texas Pediatric Patient Derived Xenograft </t>
+  </si>
+  <si>
+    <t>phs003215</t>
+  </si>
+  <si>
+    <t>phs003215.v1.p1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,6 +229,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF172B4D"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -269,7 +284,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -298,6 +313,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -921,13 +937,27 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.4">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
+      <c r="A13" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="13">
+        <v>51</v>
+      </c>
+      <c r="F13" s="13">
+        <v>362</v>
+      </c>
+      <c r="G13" s="13">
+        <v>620</v>
+      </c>
     </row>
     <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.4">
       <c r="A14" s="11"/>
